--- a/data/sars/keys/fishery_key_raw.xlsx
+++ b/data/sars/keys/fishery_key_raw.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/keys/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8D3DD70-F169-384C-BA31-A6EFDE3BE3E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4413C67-FD84-5849-88F5-48F00CE2048F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="500" windowWidth="27640" windowHeight="16940" xr2:uid="{49FC6871-2754-3C4C-92D2-E10D521CB789}"/>
+    <workbookView xWindow="900" yWindow="500" windowWidth="30840" windowHeight="20820" xr2:uid="{49FC6871-2754-3C4C-92D2-E10D521CB789}"/>
   </bookViews>
   <sheets>
     <sheet name="fishery_key_raw" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">fishery_key_raw!$A$1:$C$672</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">fishery_key_raw!$A$1:$D$672</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2016" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2137" uniqueCount="693">
   <si>
     <t>region_orig</t>
   </si>
@@ -2069,6 +2069,39 @@
   </si>
   <si>
     <t>Unknown</t>
+  </si>
+  <si>
+    <t>fishery_orig</t>
+  </si>
+  <si>
+    <t>AK/WA/OR/CA CPFV</t>
+  </si>
+  <si>
+    <t>AK BSAI pollock trawl</t>
+  </si>
+  <si>
+    <t>CA halibut/white seabass and other species set gillnet (&gt;3.5" mesh)</t>
+  </si>
+  <si>
+    <t>CA angel shark/halibut and other species set gillnet (&gt;3.5" mesh)</t>
+  </si>
+  <si>
+    <t>CA set gillnet (mesh size &lt;3.5")</t>
+  </si>
+  <si>
+    <t>CA set and drift gillnet (mesh size &lt;3.5")</t>
+  </si>
+  <si>
+    <t>CA thresher shark/swordfish drift gillnet (&gt;14" mesh)</t>
+  </si>
+  <si>
+    <t>CA yellowtail, barracuda, and white seabass drift gillnet (3.5-14" mesh size)</t>
+  </si>
+  <si>
+    <t>CA/OR thresher shark/swordfish drift gillnet (&gt;14" mesh size)</t>
+  </si>
+  <si>
+    <t>CA longline</t>
   </si>
 </sst>
 </file>
@@ -2930,15 +2963,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{176C812C-05FE-6A4B-9762-43F5FB22FFF3}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:C672"/>
+  <dimension ref="A1:D672"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="165.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="90.1640625" customWidth="1"/>
+    <col min="4" max="4" width="57.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2946,10 +2980,13 @@
         <v>676</v>
       </c>
       <c r="C1" t="s">
+        <v>682</v>
+      </c>
+      <c r="D1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2960,7 +2997,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2971,7 +3008,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -2982,7 +3019,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -2993,7 +3030,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -3004,7 +3041,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -3015,7 +3052,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -3026,7 +3063,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -3037,7 +3074,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -3048,7 +3085,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>2</v>
       </c>
@@ -3059,7 +3096,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -3070,7 +3107,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>2</v>
       </c>
@@ -3081,7 +3118,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -3092,7 +3129,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>2</v>
       </c>
@@ -3103,7 +3140,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>2</v>
       </c>
@@ -5226,7 +5263,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="209" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>2</v>
       </c>
@@ -5237,7 +5274,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="210" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>2</v>
       </c>
@@ -5248,7 +5285,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="211" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>2</v>
       </c>
@@ -5259,7 +5296,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="212" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>2</v>
       </c>
@@ -5270,7 +5307,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="213" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>2</v>
       </c>
@@ -5281,7 +5318,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="214" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>2</v>
       </c>
@@ -5292,7 +5329,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="215" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>2</v>
       </c>
@@ -5303,7 +5340,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="216" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>2</v>
       </c>
@@ -5314,7 +5351,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="217" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>2</v>
       </c>
@@ -5325,7 +5362,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="218" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>2</v>
       </c>
@@ -5336,7 +5373,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>220</v>
       </c>
@@ -5347,7 +5384,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>220</v>
       </c>
@@ -5358,7 +5395,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>220</v>
       </c>
@@ -5368,8 +5405,11 @@
       <c r="C221" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D221" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>220</v>
       </c>
@@ -5379,8 +5419,11 @@
       <c r="C222" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D222" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>220</v>
       </c>
@@ -5391,7 +5434,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>220</v>
       </c>
@@ -5402,7 +5445,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>220</v>
       </c>
@@ -5413,29 +5456,35 @@
         <v>227</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
-        <v>220</v>
+        <v>247</v>
       </c>
       <c r="B226" t="s">
         <v>679</v>
       </c>
       <c r="C226" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.2">
+        <v>424</v>
+      </c>
+      <c r="D226" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>220</v>
+        <v>247</v>
       </c>
       <c r="B227" t="s">
         <v>679</v>
       </c>
       <c r="C227" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.2">
+        <v>429</v>
+      </c>
+      <c r="D227" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>220</v>
       </c>
@@ -5446,7 +5495,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>220</v>
       </c>
@@ -5457,7 +5506,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>220</v>
       </c>
@@ -5468,7 +5517,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>220</v>
       </c>
@@ -5479,7 +5528,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>220</v>
       </c>
@@ -5489,8 +5538,11 @@
       <c r="C232" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D232" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>220</v>
       </c>
@@ -5501,7 +5553,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>220</v>
       </c>
@@ -5512,7 +5564,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>220</v>
       </c>
@@ -5523,7 +5575,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>220</v>
       </c>
@@ -5534,7 +5586,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>220</v>
       </c>
@@ -5545,7 +5597,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>220</v>
       </c>
@@ -5556,7 +5608,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>220</v>
       </c>
@@ -5567,7 +5619,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>220</v>
       </c>
@@ -5578,7 +5630,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>220</v>
       </c>
@@ -5589,7 +5641,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>220</v>
       </c>
@@ -5600,7 +5652,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>220</v>
       </c>
@@ -5611,7 +5663,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>220</v>
       </c>
@@ -5630,7 +5682,7 @@
         <v>677</v>
       </c>
       <c r="C245" t="s">
-        <v>248</v>
+        <v>346</v>
       </c>
     </row>
     <row r="246" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -5641,7 +5693,7 @@
         <v>677</v>
       </c>
       <c r="C246" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="247" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -5652,7 +5704,7 @@
         <v>677</v>
       </c>
       <c r="C247" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="248" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -5663,7 +5715,7 @@
         <v>677</v>
       </c>
       <c r="C248" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="249" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -5674,7 +5726,7 @@
         <v>677</v>
       </c>
       <c r="C249" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="250" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -5685,7 +5737,7 @@
         <v>677</v>
       </c>
       <c r="C250" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="251" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -5696,7 +5748,7 @@
         <v>677</v>
       </c>
       <c r="C251" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="252" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -5707,7 +5759,7 @@
         <v>677</v>
       </c>
       <c r="C252" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
     </row>
     <row r="253" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -5718,7 +5770,7 @@
         <v>677</v>
       </c>
       <c r="C253" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="254" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -5729,7 +5781,7 @@
         <v>677</v>
       </c>
       <c r="C254" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="255" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -5740,7 +5792,7 @@
         <v>677</v>
       </c>
       <c r="C255" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="256" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -5751,183 +5803,189 @@
         <v>677</v>
       </c>
       <c r="C256" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A257" t="s">
+        <v>247</v>
+      </c>
+      <c r="B257" t="s">
+        <v>677</v>
+      </c>
+      <c r="C257" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A258" t="s">
+        <v>247</v>
+      </c>
+      <c r="B258" t="s">
+        <v>677</v>
+      </c>
+      <c r="C258" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A259" t="s">
+        <v>247</v>
+      </c>
+      <c r="B259" t="s">
+        <v>677</v>
+      </c>
+      <c r="C259" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A260" t="s">
+        <v>247</v>
+      </c>
+      <c r="B260" t="s">
+        <v>677</v>
+      </c>
+      <c r="C260" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A261" t="s">
+        <v>247</v>
+      </c>
+      <c r="B261" t="s">
+        <v>677</v>
+      </c>
+      <c r="C261" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A262" t="s">
+        <v>247</v>
+      </c>
+      <c r="B262" t="s">
+        <v>677</v>
+      </c>
+      <c r="C262" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A263" t="s">
+        <v>247</v>
+      </c>
+      <c r="B263" t="s">
+        <v>677</v>
+      </c>
+      <c r="C263" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A264" t="s">
+        <v>247</v>
+      </c>
+      <c r="B264" t="s">
+        <v>677</v>
+      </c>
+      <c r="C264" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A265" t="s">
+        <v>247</v>
+      </c>
+      <c r="B265" t="s">
+        <v>677</v>
+      </c>
+      <c r="C265" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="257" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A257" t="s">
-        <v>247</v>
-      </c>
-      <c r="B257" t="s">
-        <v>677</v>
-      </c>
-      <c r="C257" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A258" t="s">
-        <v>247</v>
-      </c>
-      <c r="B258" t="s">
-        <v>677</v>
-      </c>
-      <c r="C258" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A259" t="s">
-        <v>247</v>
-      </c>
-      <c r="B259" t="s">
-        <v>677</v>
-      </c>
-      <c r="C259" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A260" t="s">
-        <v>247</v>
-      </c>
-      <c r="B260" t="s">
-        <v>677</v>
-      </c>
-      <c r="C260" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="261" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A261" t="s">
-        <v>247</v>
-      </c>
-      <c r="B261" t="s">
-        <v>677</v>
-      </c>
-      <c r="C261" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="262" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A262" t="s">
-        <v>247</v>
-      </c>
-      <c r="B262" t="s">
-        <v>677</v>
-      </c>
-      <c r="C262" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="263" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A263" t="s">
-        <v>247</v>
-      </c>
-      <c r="B263" t="s">
-        <v>677</v>
-      </c>
-      <c r="C263" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="264" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A264" t="s">
-        <v>247</v>
-      </c>
-      <c r="B264" t="s">
-        <v>677</v>
-      </c>
-      <c r="C264" t="s">
+    <row r="266" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A266" t="s">
+        <v>247</v>
+      </c>
+      <c r="B266" t="s">
+        <v>677</v>
+      </c>
+      <c r="C266" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="265" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A265" t="s">
-        <v>247</v>
-      </c>
-      <c r="B265" t="s">
-        <v>677</v>
-      </c>
-      <c r="C265" t="s">
+      <c r="D266" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A267" t="s">
+        <v>247</v>
+      </c>
+      <c r="B267" t="s">
+        <v>677</v>
+      </c>
+      <c r="C267" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="266" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A266" t="s">
-        <v>247</v>
-      </c>
-      <c r="B266" t="s">
-        <v>677</v>
-      </c>
-      <c r="C266" t="s">
+      <c r="D267" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A268" t="s">
+        <v>247</v>
+      </c>
+      <c r="B268" t="s">
+        <v>677</v>
+      </c>
+      <c r="C268" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="267" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A267" t="s">
-        <v>247</v>
-      </c>
-      <c r="B267" t="s">
-        <v>677</v>
-      </c>
-      <c r="C267" t="s">
+    <row r="269" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A269" t="s">
+        <v>247</v>
+      </c>
+      <c r="B269" t="s">
+        <v>677</v>
+      </c>
+      <c r="C269" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="268" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A268" t="s">
-        <v>247</v>
-      </c>
-      <c r="B268" t="s">
-        <v>677</v>
-      </c>
-      <c r="C268" t="s">
+    <row r="270" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A270" t="s">
+        <v>247</v>
+      </c>
+      <c r="B270" t="s">
+        <v>677</v>
+      </c>
+      <c r="C270" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="269" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A269" t="s">
-        <v>247</v>
-      </c>
-      <c r="B269" t="s">
-        <v>677</v>
-      </c>
-      <c r="C269" t="s">
+    <row r="271" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A271" t="s">
+        <v>247</v>
+      </c>
+      <c r="B271" t="s">
+        <v>677</v>
+      </c>
+      <c r="C271" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="270" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A270" t="s">
-        <v>247</v>
-      </c>
-      <c r="B270" t="s">
-        <v>677</v>
-      </c>
-      <c r="C270" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="271" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A271" t="s">
-        <v>247</v>
-      </c>
-      <c r="B271" t="s">
-        <v>677</v>
-      </c>
-      <c r="C271" t="s">
+    <row r="272" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A272" t="s">
+        <v>247</v>
+      </c>
+      <c r="B272" t="s">
+        <v>677</v>
+      </c>
+      <c r="C272" t="s">
         <v>274</v>
-      </c>
-    </row>
-    <row r="272" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A272" t="s">
-        <v>247</v>
-      </c>
-      <c r="B272" t="s">
-        <v>677</v>
-      </c>
-      <c r="C272" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="273" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -5938,7 +5996,7 @@
         <v>677</v>
       </c>
       <c r="C273" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="274" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -5949,7 +6007,7 @@
         <v>677</v>
       </c>
       <c r="C274" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="275" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -5960,7 +6018,7 @@
         <v>677</v>
       </c>
       <c r="C275" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="276" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -5971,7 +6029,7 @@
         <v>677</v>
       </c>
       <c r="C276" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="277" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -5982,7 +6040,7 @@
         <v>677</v>
       </c>
       <c r="C277" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="278" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -5993,7 +6051,7 @@
         <v>677</v>
       </c>
       <c r="C278" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="279" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6004,7 +6062,7 @@
         <v>677</v>
       </c>
       <c r="C279" t="s">
-        <v>282</v>
+        <v>347</v>
       </c>
     </row>
     <row r="280" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6015,7 +6073,7 @@
         <v>677</v>
       </c>
       <c r="C280" t="s">
-        <v>283</v>
+        <v>348</v>
       </c>
     </row>
     <row r="281" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6026,7 +6084,7 @@
         <v>677</v>
       </c>
       <c r="C281" t="s">
-        <v>284</v>
+        <v>349</v>
       </c>
     </row>
     <row r="282" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6037,7 +6095,7 @@
         <v>677</v>
       </c>
       <c r="C282" t="s">
-        <v>285</v>
+        <v>350</v>
       </c>
     </row>
     <row r="283" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6048,7 +6106,7 @@
         <v>677</v>
       </c>
       <c r="C283" t="s">
-        <v>286</v>
+        <v>351</v>
       </c>
     </row>
     <row r="284" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6059,7 +6117,7 @@
         <v>677</v>
       </c>
       <c r="C284" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="285" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6070,7 +6128,7 @@
         <v>677</v>
       </c>
       <c r="C285" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="286" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6081,7 +6139,7 @@
         <v>677</v>
       </c>
       <c r="C286" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
     </row>
     <row r="287" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6092,7 +6150,7 @@
         <v>677</v>
       </c>
       <c r="C287" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="288" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6103,7 +6161,7 @@
         <v>677</v>
       </c>
       <c r="C288" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
     </row>
     <row r="289" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6114,7 +6172,7 @@
         <v>677</v>
       </c>
       <c r="C289" t="s">
-        <v>292</v>
+        <v>352</v>
       </c>
     </row>
     <row r="290" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6125,7 +6183,7 @@
         <v>677</v>
       </c>
       <c r="C290" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
     </row>
     <row r="291" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6136,7 +6194,7 @@
         <v>677</v>
       </c>
       <c r="C291" t="s">
-        <v>294</v>
+        <v>353</v>
       </c>
     </row>
     <row r="292" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6147,7 +6205,7 @@
         <v>677</v>
       </c>
       <c r="C292" t="s">
-        <v>295</v>
+        <v>354</v>
       </c>
     </row>
     <row r="293" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6158,7 +6216,7 @@
         <v>677</v>
       </c>
       <c r="C293" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
     </row>
     <row r="294" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6169,7 +6227,7 @@
         <v>677</v>
       </c>
       <c r="C294" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
     </row>
     <row r="295" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6180,7 +6238,7 @@
         <v>677</v>
       </c>
       <c r="C295" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
     </row>
     <row r="296" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6191,7 +6249,7 @@
         <v>677</v>
       </c>
       <c r="C296" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
     </row>
     <row r="297" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6202,7 +6260,7 @@
         <v>677</v>
       </c>
       <c r="C297" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="298" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6213,7 +6271,7 @@
         <v>677</v>
       </c>
       <c r="C298" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
     </row>
     <row r="299" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6224,7 +6282,7 @@
         <v>677</v>
       </c>
       <c r="C299" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
     </row>
     <row r="300" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6235,7 +6293,7 @@
         <v>677</v>
       </c>
       <c r="C300" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
     </row>
     <row r="301" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6246,7 +6304,7 @@
         <v>677</v>
       </c>
       <c r="C301" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
     </row>
     <row r="302" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6257,7 +6315,7 @@
         <v>677</v>
       </c>
       <c r="C302" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
     </row>
     <row r="303" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6268,7 +6326,7 @@
         <v>677</v>
       </c>
       <c r="C303" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
     </row>
     <row r="304" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6279,7 +6337,7 @@
         <v>677</v>
       </c>
       <c r="C304" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
     </row>
     <row r="305" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6290,7 +6348,7 @@
         <v>677</v>
       </c>
       <c r="C305" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
     </row>
     <row r="306" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6301,7 +6359,7 @@
         <v>677</v>
       </c>
       <c r="C306" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
     </row>
     <row r="307" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6312,7 +6370,7 @@
         <v>677</v>
       </c>
       <c r="C307" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
     </row>
     <row r="308" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6323,7 +6381,7 @@
         <v>677</v>
       </c>
       <c r="C308" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
     </row>
     <row r="309" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6334,7 +6392,7 @@
         <v>677</v>
       </c>
       <c r="C309" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
     </row>
     <row r="310" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6345,7 +6403,7 @@
         <v>677</v>
       </c>
       <c r="C310" t="s">
-        <v>313</v>
+        <v>355</v>
       </c>
     </row>
     <row r="311" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6356,7 +6414,7 @@
         <v>677</v>
       </c>
       <c r="C311" t="s">
-        <v>314</v>
+        <v>356</v>
       </c>
     </row>
     <row r="312" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6367,7 +6425,7 @@
         <v>677</v>
       </c>
       <c r="C312" t="s">
-        <v>315</v>
+        <v>357</v>
       </c>
     </row>
     <row r="313" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6378,7 +6436,7 @@
         <v>677</v>
       </c>
       <c r="C313" t="s">
-        <v>316</v>
+        <v>358</v>
       </c>
     </row>
     <row r="314" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6389,7 +6447,7 @@
         <v>677</v>
       </c>
       <c r="C314" t="s">
-        <v>317</v>
+        <v>359</v>
       </c>
     </row>
     <row r="315" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6400,7 +6458,7 @@
         <v>677</v>
       </c>
       <c r="C315" t="s">
-        <v>318</v>
+        <v>360</v>
       </c>
     </row>
     <row r="316" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6411,7 +6469,7 @@
         <v>677</v>
       </c>
       <c r="C316" t="s">
-        <v>319</v>
+        <v>361</v>
       </c>
     </row>
     <row r="317" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6422,7 +6480,7 @@
         <v>677</v>
       </c>
       <c r="C317" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
     </row>
     <row r="318" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6433,7 +6491,7 @@
         <v>677</v>
       </c>
       <c r="C318" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
     </row>
     <row r="319" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6444,7 +6502,7 @@
         <v>677</v>
       </c>
       <c r="C319" t="s">
-        <v>322</v>
+        <v>306</v>
       </c>
     </row>
     <row r="320" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6455,7 +6513,7 @@
         <v>677</v>
       </c>
       <c r="C320" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
     </row>
     <row r="321" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6466,7 +6524,7 @@
         <v>677</v>
       </c>
       <c r="C321" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
     </row>
     <row r="322" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6477,7 +6535,7 @@
         <v>677</v>
       </c>
       <c r="C322" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
     </row>
     <row r="323" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6488,7 +6546,7 @@
         <v>677</v>
       </c>
       <c r="C323" t="s">
-        <v>326</v>
+        <v>310</v>
       </c>
     </row>
     <row r="324" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6499,7 +6557,7 @@
         <v>677</v>
       </c>
       <c r="C324" t="s">
-        <v>327</v>
+        <v>311</v>
       </c>
     </row>
     <row r="325" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6510,7 +6568,7 @@
         <v>677</v>
       </c>
       <c r="C325" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
     </row>
     <row r="326" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6521,7 +6579,7 @@
         <v>677</v>
       </c>
       <c r="C326" t="s">
-        <v>329</v>
+        <v>362</v>
       </c>
     </row>
     <row r="327" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6532,7 +6590,7 @@
         <v>677</v>
       </c>
       <c r="C327" t="s">
-        <v>330</v>
+        <v>363</v>
       </c>
     </row>
     <row r="328" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6543,7 +6601,7 @@
         <v>677</v>
       </c>
       <c r="C328" t="s">
-        <v>331</v>
+        <v>364</v>
       </c>
     </row>
     <row r="329" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6554,7 +6612,7 @@
         <v>677</v>
       </c>
       <c r="C329" t="s">
-        <v>332</v>
+        <v>365</v>
       </c>
     </row>
     <row r="330" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6565,7 +6623,7 @@
         <v>677</v>
       </c>
       <c r="C330" t="s">
-        <v>333</v>
+        <v>366</v>
       </c>
     </row>
     <row r="331" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6576,7 +6634,7 @@
         <v>677</v>
       </c>
       <c r="C331" t="s">
-        <v>334</v>
+        <v>367</v>
       </c>
     </row>
     <row r="332" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6587,7 +6645,7 @@
         <v>677</v>
       </c>
       <c r="C332" t="s">
-        <v>335</v>
+        <v>368</v>
       </c>
     </row>
     <row r="333" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6598,7 +6656,7 @@
         <v>677</v>
       </c>
       <c r="C333" t="s">
-        <v>336</v>
+        <v>369</v>
       </c>
     </row>
     <row r="334" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6609,7 +6667,7 @@
         <v>677</v>
       </c>
       <c r="C334" t="s">
-        <v>337</v>
+        <v>370</v>
       </c>
     </row>
     <row r="335" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6620,7 +6678,7 @@
         <v>677</v>
       </c>
       <c r="C335" t="s">
-        <v>338</v>
+        <v>371</v>
       </c>
     </row>
     <row r="336" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6631,7 +6689,7 @@
         <v>677</v>
       </c>
       <c r="C336" t="s">
-        <v>339</v>
+        <v>372</v>
       </c>
     </row>
     <row r="337" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6642,7 +6700,7 @@
         <v>677</v>
       </c>
       <c r="C337" t="s">
-        <v>340</v>
+        <v>313</v>
       </c>
     </row>
     <row r="338" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6653,7 +6711,7 @@
         <v>677</v>
       </c>
       <c r="C338" t="s">
-        <v>341</v>
+        <v>314</v>
       </c>
     </row>
     <row r="339" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6664,7 +6722,7 @@
         <v>677</v>
       </c>
       <c r="C339" t="s">
-        <v>342</v>
+        <v>315</v>
       </c>
     </row>
     <row r="340" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6675,7 +6733,7 @@
         <v>677</v>
       </c>
       <c r="C340" t="s">
-        <v>343</v>
+        <v>373</v>
       </c>
     </row>
     <row r="341" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6686,7 +6744,7 @@
         <v>677</v>
       </c>
       <c r="C341" t="s">
-        <v>344</v>
+        <v>316</v>
       </c>
     </row>
     <row r="342" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6697,7 +6755,7 @@
         <v>677</v>
       </c>
       <c r="C342" t="s">
-        <v>345</v>
+        <v>374</v>
       </c>
     </row>
     <row r="343" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6708,7 +6766,7 @@
         <v>677</v>
       </c>
       <c r="C343" t="s">
-        <v>346</v>
+        <v>375</v>
       </c>
     </row>
     <row r="344" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6719,7 +6777,7 @@
         <v>677</v>
       </c>
       <c r="C344" t="s">
-        <v>347</v>
+        <v>317</v>
       </c>
     </row>
     <row r="345" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6730,7 +6788,7 @@
         <v>677</v>
       </c>
       <c r="C345" t="s">
-        <v>348</v>
+        <v>318</v>
       </c>
     </row>
     <row r="346" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6741,7 +6799,7 @@
         <v>677</v>
       </c>
       <c r="C346" t="s">
-        <v>349</v>
+        <v>319</v>
       </c>
     </row>
     <row r="347" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6752,7 +6810,7 @@
         <v>677</v>
       </c>
       <c r="C347" t="s">
-        <v>350</v>
+        <v>320</v>
       </c>
     </row>
     <row r="348" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6763,7 +6821,7 @@
         <v>677</v>
       </c>
       <c r="C348" t="s">
-        <v>351</v>
+        <v>381</v>
       </c>
     </row>
     <row r="349" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6774,7 +6832,7 @@
         <v>677</v>
       </c>
       <c r="C349" t="s">
-        <v>352</v>
+        <v>380</v>
       </c>
     </row>
     <row r="350" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6785,7 +6843,7 @@
         <v>677</v>
       </c>
       <c r="C350" t="s">
-        <v>353</v>
+        <v>376</v>
       </c>
     </row>
     <row r="351" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6796,7 +6854,7 @@
         <v>677</v>
       </c>
       <c r="C351" t="s">
-        <v>354</v>
+        <v>377</v>
       </c>
     </row>
     <row r="352" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6807,7 +6865,7 @@
         <v>677</v>
       </c>
       <c r="C352" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
     </row>
     <row r="353" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6818,7 +6876,7 @@
         <v>677</v>
       </c>
       <c r="C353" t="s">
-        <v>356</v>
+        <v>379</v>
       </c>
     </row>
     <row r="354" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6829,7 +6887,7 @@
         <v>677</v>
       </c>
       <c r="C354" t="s">
-        <v>357</v>
+        <v>382</v>
       </c>
     </row>
     <row r="355" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6840,7 +6898,7 @@
         <v>677</v>
       </c>
       <c r="C355" t="s">
-        <v>358</v>
+        <v>383</v>
       </c>
     </row>
     <row r="356" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6851,7 +6909,7 @@
         <v>677</v>
       </c>
       <c r="C356" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
     </row>
     <row r="357" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6862,7 +6920,7 @@
         <v>677</v>
       </c>
       <c r="C357" t="s">
-        <v>360</v>
+        <v>322</v>
       </c>
     </row>
     <row r="358" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6873,7 +6931,7 @@
         <v>677</v>
       </c>
       <c r="C358" t="s">
-        <v>361</v>
+        <v>323</v>
       </c>
     </row>
     <row r="359" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6884,7 +6942,7 @@
         <v>677</v>
       </c>
       <c r="C359" t="s">
-        <v>362</v>
+        <v>324</v>
       </c>
     </row>
     <row r="360" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6895,7 +6953,7 @@
         <v>677</v>
       </c>
       <c r="C360" t="s">
-        <v>363</v>
+        <v>325</v>
       </c>
     </row>
     <row r="361" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6906,7 +6964,7 @@
         <v>677</v>
       </c>
       <c r="C361" t="s">
-        <v>364</v>
+        <v>326</v>
       </c>
     </row>
     <row r="362" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6917,7 +6975,7 @@
         <v>677</v>
       </c>
       <c r="C362" t="s">
-        <v>365</v>
+        <v>327</v>
       </c>
     </row>
     <row r="363" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6928,7 +6986,7 @@
         <v>677</v>
       </c>
       <c r="C363" t="s">
-        <v>366</v>
+        <v>328</v>
       </c>
     </row>
     <row r="364" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6939,7 +6997,7 @@
         <v>677</v>
       </c>
       <c r="C364" t="s">
-        <v>367</v>
+        <v>329</v>
       </c>
     </row>
     <row r="365" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6950,7 +7008,7 @@
         <v>677</v>
       </c>
       <c r="C365" t="s">
-        <v>368</v>
+        <v>330</v>
       </c>
     </row>
     <row r="366" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6961,7 +7019,7 @@
         <v>677</v>
       </c>
       <c r="C366" t="s">
-        <v>369</v>
+        <v>331</v>
       </c>
     </row>
     <row r="367" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6972,7 +7030,7 @@
         <v>677</v>
       </c>
       <c r="C367" t="s">
-        <v>370</v>
+        <v>332</v>
       </c>
     </row>
     <row r="368" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6983,7 +7041,7 @@
         <v>677</v>
       </c>
       <c r="C368" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
     </row>
     <row r="369" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -6994,7 +7052,7 @@
         <v>677</v>
       </c>
       <c r="C369" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
     </row>
     <row r="370" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7005,7 +7063,7 @@
         <v>677</v>
       </c>
       <c r="C370" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
     </row>
     <row r="371" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7016,7 +7074,7 @@
         <v>677</v>
       </c>
       <c r="C371" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
     </row>
     <row r="372" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7027,7 +7085,7 @@
         <v>677</v>
       </c>
       <c r="C372" t="s">
-        <v>375</v>
+        <v>389</v>
       </c>
     </row>
     <row r="373" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7038,7 +7096,7 @@
         <v>677</v>
       </c>
       <c r="C373" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
     </row>
     <row r="374" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7049,7 +7107,7 @@
         <v>677</v>
       </c>
       <c r="C374" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
     </row>
     <row r="375" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7060,7 +7118,7 @@
         <v>677</v>
       </c>
       <c r="C375" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
     </row>
     <row r="376" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7071,7 +7129,7 @@
         <v>677</v>
       </c>
       <c r="C376" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
     </row>
     <row r="377" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7082,7 +7140,7 @@
         <v>677</v>
       </c>
       <c r="C377" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
     </row>
     <row r="378" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7093,7 +7151,7 @@
         <v>677</v>
       </c>
       <c r="C378" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
     </row>
     <row r="379" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7104,7 +7162,7 @@
         <v>677</v>
       </c>
       <c r="C379" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
     </row>
     <row r="380" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7115,7 +7173,7 @@
         <v>677</v>
       </c>
       <c r="C380" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
     </row>
     <row r="381" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7126,7 +7184,7 @@
         <v>677</v>
       </c>
       <c r="C381" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
     </row>
     <row r="382" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7137,7 +7195,7 @@
         <v>677</v>
       </c>
       <c r="C382" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
     </row>
     <row r="383" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7148,7 +7206,7 @@
         <v>677</v>
       </c>
       <c r="C383" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
     </row>
     <row r="384" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7159,7 +7217,7 @@
         <v>677</v>
       </c>
       <c r="C384" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
     </row>
     <row r="385" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7170,7 +7228,7 @@
         <v>677</v>
       </c>
       <c r="C385" t="s">
-        <v>388</v>
+        <v>333</v>
       </c>
     </row>
     <row r="386" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7181,7 +7239,7 @@
         <v>677</v>
       </c>
       <c r="C386" t="s">
-        <v>389</v>
+        <v>334</v>
       </c>
     </row>
     <row r="387" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7192,7 +7250,7 @@
         <v>677</v>
       </c>
       <c r="C387" t="s">
-        <v>390</v>
+        <v>335</v>
       </c>
     </row>
     <row r="388" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7203,7 +7261,7 @@
         <v>677</v>
       </c>
       <c r="C388" t="s">
-        <v>391</v>
+        <v>336</v>
       </c>
     </row>
     <row r="389" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7214,7 +7272,7 @@
         <v>677</v>
       </c>
       <c r="C389" t="s">
-        <v>392</v>
+        <v>337</v>
       </c>
     </row>
     <row r="390" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7225,7 +7283,7 @@
         <v>677</v>
       </c>
       <c r="C390" t="s">
-        <v>393</v>
+        <v>338</v>
       </c>
     </row>
     <row r="391" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7236,7 +7294,7 @@
         <v>677</v>
       </c>
       <c r="C391" t="s">
-        <v>394</v>
+        <v>339</v>
       </c>
     </row>
     <row r="392" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7247,7 +7305,7 @@
         <v>677</v>
       </c>
       <c r="C392" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="393" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7258,7 +7316,7 @@
         <v>677</v>
       </c>
       <c r="C393" t="s">
-        <v>396</v>
+        <v>340</v>
       </c>
     </row>
     <row r="394" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7269,7 +7327,7 @@
         <v>677</v>
       </c>
       <c r="C394" t="s">
-        <v>397</v>
+        <v>341</v>
       </c>
     </row>
     <row r="395" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7280,7 +7338,7 @@
         <v>677</v>
       </c>
       <c r="C395" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="396" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7291,7 +7349,7 @@
         <v>677</v>
       </c>
       <c r="C396" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="397" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7302,7 +7360,7 @@
         <v>677</v>
       </c>
       <c r="C397" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="398" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7313,7 +7371,7 @@
         <v>677</v>
       </c>
       <c r="C398" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="399" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7324,7 +7382,7 @@
         <v>677</v>
       </c>
       <c r="C399" t="s">
-        <v>402</v>
+        <v>342</v>
       </c>
     </row>
     <row r="400" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
@@ -7335,10 +7393,10 @@
         <v>677</v>
       </c>
       <c r="C400" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="401" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
         <v>247</v>
       </c>
@@ -7346,10 +7404,10 @@
         <v>677</v>
       </c>
       <c r="C401" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="402" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
         <v>247</v>
       </c>
@@ -7357,10 +7415,10 @@
         <v>677</v>
       </c>
       <c r="C402" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="403" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
         <v>247</v>
       </c>
@@ -7368,10 +7426,10 @@
         <v>677</v>
       </c>
       <c r="C403" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="404" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
         <v>247</v>
       </c>
@@ -7379,10 +7437,10 @@
         <v>677</v>
       </c>
       <c r="C404" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="405" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
         <v>247</v>
       </c>
@@ -7390,10 +7448,10 @@
         <v>677</v>
       </c>
       <c r="C405" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="406" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
         <v>247</v>
       </c>
@@ -7401,10 +7459,10 @@
         <v>677</v>
       </c>
       <c r="C406" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="407" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
         <v>247</v>
       </c>
@@ -7412,10 +7470,10 @@
         <v>677</v>
       </c>
       <c r="C407" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="408" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
         <v>247</v>
       </c>
@@ -7423,10 +7481,10 @@
         <v>677</v>
       </c>
       <c r="C408" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="409" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
         <v>247</v>
       </c>
@@ -7434,10 +7492,10 @@
         <v>677</v>
       </c>
       <c r="C409" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="410" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
         <v>247</v>
       </c>
@@ -7445,10 +7503,10 @@
         <v>677</v>
       </c>
       <c r="C410" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="411" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
         <v>247</v>
       </c>
@@ -7456,10 +7514,10 @@
         <v>677</v>
       </c>
       <c r="C411" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="412" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
         <v>247</v>
       </c>
@@ -7470,7 +7528,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="413" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
         <v>247</v>
       </c>
@@ -7480,8 +7538,11 @@
       <c r="C413" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="414" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="D413" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
         <v>247</v>
       </c>
@@ -7491,8 +7552,11 @@
       <c r="C414" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="415" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="D414" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
         <v>247</v>
       </c>
@@ -7502,8 +7566,11 @@
       <c r="C415" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="416" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="D415" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
         <v>247</v>
       </c>
@@ -7514,7 +7581,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="417" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
         <v>247</v>
       </c>
@@ -7525,7 +7592,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="418" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
         <v>247</v>
       </c>
@@ -7536,7 +7603,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="419" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
         <v>247</v>
       </c>
@@ -7547,7 +7614,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="420" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
         <v>247</v>
       </c>
@@ -7558,7 +7625,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="421" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
         <v>247</v>
       </c>
@@ -7566,10 +7633,13 @@
         <v>679</v>
       </c>
       <c r="C421" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="422" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>430</v>
+      </c>
+      <c r="D421" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
         <v>247</v>
       </c>
@@ -7580,7 +7650,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="423" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
         <v>247</v>
       </c>
@@ -7588,593 +7658,755 @@
         <v>679</v>
       </c>
       <c r="C423" t="s">
+        <v>431</v>
+      </c>
+      <c r="D423" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A424" t="s">
+        <v>247</v>
+      </c>
+      <c r="B424" t="s">
+        <v>679</v>
+      </c>
+      <c r="C424" t="s">
+        <v>432</v>
+      </c>
+      <c r="D424" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A425" t="s">
+        <v>247</v>
+      </c>
+      <c r="B425" t="s">
+        <v>679</v>
+      </c>
+      <c r="C425" t="s">
+        <v>433</v>
+      </c>
+      <c r="D425" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A426" t="s">
+        <v>247</v>
+      </c>
+      <c r="B426" t="s">
+        <v>679</v>
+      </c>
+      <c r="C426" t="s">
+        <v>434</v>
+      </c>
+      <c r="D426" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A427" t="s">
+        <v>247</v>
+      </c>
+      <c r="B427" t="s">
+        <v>679</v>
+      </c>
+      <c r="C427" t="s">
+        <v>435</v>
+      </c>
+      <c r="D427" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A428" t="s">
+        <v>247</v>
+      </c>
+      <c r="B428" t="s">
+        <v>679</v>
+      </c>
+      <c r="C428" t="s">
+        <v>436</v>
+      </c>
+      <c r="D428" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A429" t="s">
+        <v>247</v>
+      </c>
+      <c r="B429" t="s">
+        <v>679</v>
+      </c>
+      <c r="C429" t="s">
+        <v>437</v>
+      </c>
+      <c r="D429" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A430" t="s">
+        <v>247</v>
+      </c>
+      <c r="B430" t="s">
+        <v>679</v>
+      </c>
+      <c r="C430" t="s">
+        <v>438</v>
+      </c>
+      <c r="D430" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A431" t="s">
+        <v>247</v>
+      </c>
+      <c r="B431" t="s">
+        <v>679</v>
+      </c>
+      <c r="C431" t="s">
+        <v>439</v>
+      </c>
+      <c r="D431" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A432" t="s">
+        <v>247</v>
+      </c>
+      <c r="B432" t="s">
+        <v>679</v>
+      </c>
+      <c r="C432" t="s">
+        <v>440</v>
+      </c>
+      <c r="D432" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A433" t="s">
+        <v>247</v>
+      </c>
+      <c r="B433" t="s">
+        <v>679</v>
+      </c>
+      <c r="C433" t="s">
+        <v>441</v>
+      </c>
+      <c r="D433" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A434" t="s">
+        <v>247</v>
+      </c>
+      <c r="B434" t="s">
+        <v>679</v>
+      </c>
+      <c r="C434" t="s">
+        <v>442</v>
+      </c>
+      <c r="D434" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="435" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A435" t="s">
+        <v>247</v>
+      </c>
+      <c r="B435" t="s">
+        <v>679</v>
+      </c>
+      <c r="C435" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="424" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A424" t="s">
-        <v>247</v>
-      </c>
-      <c r="B424" t="s">
-        <v>679</v>
-      </c>
-      <c r="C424" t="s">
+      <c r="D435" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A436" t="s">
+        <v>247</v>
+      </c>
+      <c r="B436" t="s">
+        <v>679</v>
+      </c>
+      <c r="C436" t="s">
+        <v>443</v>
+      </c>
+      <c r="D436" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A437" t="s">
+        <v>247</v>
+      </c>
+      <c r="B437" t="s">
+        <v>679</v>
+      </c>
+      <c r="C437" t="s">
+        <v>444</v>
+      </c>
+      <c r="D437" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A438" t="s">
+        <v>247</v>
+      </c>
+      <c r="B438" t="s">
+        <v>679</v>
+      </c>
+      <c r="C438" t="s">
+        <v>445</v>
+      </c>
+      <c r="D438" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A439" t="s">
+        <v>247</v>
+      </c>
+      <c r="B439" t="s">
+        <v>679</v>
+      </c>
+      <c r="C439" t="s">
+        <v>446</v>
+      </c>
+      <c r="D439" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A440" t="s">
+        <v>247</v>
+      </c>
+      <c r="B440" t="s">
+        <v>679</v>
+      </c>
+      <c r="C440" t="s">
+        <v>447</v>
+      </c>
+      <c r="D440" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="441" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A441" t="s">
+        <v>247</v>
+      </c>
+      <c r="B441" t="s">
+        <v>679</v>
+      </c>
+      <c r="C441" t="s">
+        <v>448</v>
+      </c>
+      <c r="D441" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A442" t="s">
+        <v>247</v>
+      </c>
+      <c r="B442" t="s">
+        <v>679</v>
+      </c>
+      <c r="C442" t="s">
+        <v>449</v>
+      </c>
+      <c r="D442" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A443" t="s">
+        <v>247</v>
+      </c>
+      <c r="B443" t="s">
+        <v>679</v>
+      </c>
+      <c r="C443" t="s">
+        <v>450</v>
+      </c>
+      <c r="D443" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A444" t="s">
+        <v>247</v>
+      </c>
+      <c r="B444" t="s">
+        <v>679</v>
+      </c>
+      <c r="C444" t="s">
+        <v>451</v>
+      </c>
+      <c r="D444" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A445" t="s">
+        <v>247</v>
+      </c>
+      <c r="B445" t="s">
+        <v>679</v>
+      </c>
+      <c r="C445" t="s">
+        <v>454</v>
+      </c>
+      <c r="D445" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A446" t="s">
+        <v>247</v>
+      </c>
+      <c r="B446" t="s">
+        <v>679</v>
+      </c>
+      <c r="C446" t="s">
+        <v>452</v>
+      </c>
+      <c r="D446" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A447" t="s">
+        <v>247</v>
+      </c>
+      <c r="B447" t="s">
+        <v>679</v>
+      </c>
+      <c r="C447" t="s">
+        <v>453</v>
+      </c>
+      <c r="D447" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A448" t="s">
+        <v>247</v>
+      </c>
+      <c r="B448" t="s">
+        <v>679</v>
+      </c>
+      <c r="C448" t="s">
+        <v>455</v>
+      </c>
+      <c r="D448" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A449" t="s">
+        <v>247</v>
+      </c>
+      <c r="B449" t="s">
+        <v>679</v>
+      </c>
+      <c r="C449" t="s">
+        <v>456</v>
+      </c>
+      <c r="D449" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A450" t="s">
+        <v>247</v>
+      </c>
+      <c r="B450" t="s">
+        <v>679</v>
+      </c>
+      <c r="C450" t="s">
+        <v>457</v>
+      </c>
+      <c r="D450" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A451" t="s">
+        <v>247</v>
+      </c>
+      <c r="B451" t="s">
+        <v>679</v>
+      </c>
+      <c r="C451" t="s">
+        <v>458</v>
+      </c>
+      <c r="D451" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A452" t="s">
+        <v>247</v>
+      </c>
+      <c r="B452" t="s">
+        <v>679</v>
+      </c>
+      <c r="C452" t="s">
+        <v>459</v>
+      </c>
+      <c r="D452" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A453" t="s">
+        <v>247</v>
+      </c>
+      <c r="B453" t="s">
+        <v>679</v>
+      </c>
+      <c r="C453" t="s">
+        <v>460</v>
+      </c>
+      <c r="D453" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A454" t="s">
+        <v>247</v>
+      </c>
+      <c r="B454" t="s">
+        <v>679</v>
+      </c>
+      <c r="C454" t="s">
+        <v>461</v>
+      </c>
+      <c r="D454" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A455" t="s">
+        <v>247</v>
+      </c>
+      <c r="B455" t="s">
+        <v>679</v>
+      </c>
+      <c r="C455" t="s">
+        <v>462</v>
+      </c>
+      <c r="D455" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A456" t="s">
+        <v>247</v>
+      </c>
+      <c r="B456" t="s">
+        <v>679</v>
+      </c>
+      <c r="C456" t="s">
+        <v>463</v>
+      </c>
+      <c r="D456" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A457" t="s">
+        <v>247</v>
+      </c>
+      <c r="B457" t="s">
+        <v>679</v>
+      </c>
+      <c r="C457" t="s">
+        <v>464</v>
+      </c>
+      <c r="D457" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A458" t="s">
+        <v>247</v>
+      </c>
+      <c r="B458" t="s">
+        <v>679</v>
+      </c>
+      <c r="C458" t="s">
+        <v>465</v>
+      </c>
+      <c r="D458" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A459" t="s">
+        <v>247</v>
+      </c>
+      <c r="B459" t="s">
+        <v>679</v>
+      </c>
+      <c r="C459" t="s">
+        <v>466</v>
+      </c>
+      <c r="D459" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A460" t="s">
+        <v>247</v>
+      </c>
+      <c r="B460" t="s">
+        <v>679</v>
+      </c>
+      <c r="C460" t="s">
+        <v>467</v>
+      </c>
+      <c r="D460" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A461" t="s">
+        <v>247</v>
+      </c>
+      <c r="B461" t="s">
+        <v>679</v>
+      </c>
+      <c r="C461" t="s">
+        <v>468</v>
+      </c>
+      <c r="D461" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A462" t="s">
+        <v>247</v>
+      </c>
+      <c r="B462" t="s">
+        <v>679</v>
+      </c>
+      <c r="C462" t="s">
+        <v>469</v>
+      </c>
+      <c r="D462" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A463" t="s">
+        <v>247</v>
+      </c>
+      <c r="B463" t="s">
+        <v>679</v>
+      </c>
+      <c r="C463" t="s">
+        <v>470</v>
+      </c>
+      <c r="D463" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A464" t="s">
+        <v>247</v>
+      </c>
+      <c r="B464" t="s">
+        <v>679</v>
+      </c>
+      <c r="C464" t="s">
+        <v>471</v>
+      </c>
+      <c r="D464" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A465" t="s">
+        <v>247</v>
+      </c>
+      <c r="B465" t="s">
+        <v>679</v>
+      </c>
+      <c r="C465" t="s">
+        <v>472</v>
+      </c>
+      <c r="D465" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A466" t="s">
+        <v>247</v>
+      </c>
+      <c r="B466" t="s">
+        <v>679</v>
+      </c>
+      <c r="C466" t="s">
+        <v>473</v>
+      </c>
+      <c r="D466" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A467" t="s">
+        <v>247</v>
+      </c>
+      <c r="B467" t="s">
+        <v>679</v>
+      </c>
+      <c r="C467" t="s">
+        <v>474</v>
+      </c>
+      <c r="D467" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A468" t="s">
+        <v>247</v>
+      </c>
+      <c r="B468" t="s">
+        <v>679</v>
+      </c>
+      <c r="C468" t="s">
+        <v>475</v>
+      </c>
+      <c r="D468" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A469" t="s">
+        <v>247</v>
+      </c>
+      <c r="B469" t="s">
+        <v>679</v>
+      </c>
+      <c r="C469" t="s">
+        <v>476</v>
+      </c>
+      <c r="D469" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A470" t="s">
+        <v>247</v>
+      </c>
+      <c r="B470" t="s">
+        <v>679</v>
+      </c>
+      <c r="C470" t="s">
+        <v>477</v>
+      </c>
+      <c r="D470" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A471" t="s">
+        <v>247</v>
+      </c>
+      <c r="B471" t="s">
+        <v>679</v>
+      </c>
+      <c r="C471" t="s">
+        <v>478</v>
+      </c>
+      <c r="D471" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A472" t="s">
+        <v>247</v>
+      </c>
+      <c r="B472" t="s">
+        <v>679</v>
+      </c>
+      <c r="C472" t="s">
+        <v>479</v>
+      </c>
+      <c r="D472" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A473" t="s">
+        <v>247</v>
+      </c>
+      <c r="B473" t="s">
+        <v>679</v>
+      </c>
+      <c r="C473" t="s">
+        <v>480</v>
+      </c>
+      <c r="D473" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A474" t="s">
+        <v>247</v>
+      </c>
+      <c r="B474" t="s">
+        <v>679</v>
+      </c>
+      <c r="C474" t="s">
+        <v>481</v>
+      </c>
+      <c r="D474" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A475" t="s">
+        <v>247</v>
+      </c>
+      <c r="B475" t="s">
+        <v>679</v>
+      </c>
+      <c r="C475" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="425" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A425" t="s">
-        <v>247</v>
-      </c>
-      <c r="B425" t="s">
-        <v>679</v>
-      </c>
-      <c r="C425" t="s">
+      <c r="D475" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A476" t="s">
+        <v>247</v>
+      </c>
+      <c r="B476" t="s">
+        <v>679</v>
+      </c>
+      <c r="C476" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="426" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A426" t="s">
-        <v>247</v>
-      </c>
-      <c r="B426" t="s">
-        <v>679</v>
-      </c>
-      <c r="C426" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="427" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A427" t="s">
-        <v>247</v>
-      </c>
-      <c r="B427" t="s">
-        <v>679</v>
-      </c>
-      <c r="C427" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="428" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A428" t="s">
-        <v>247</v>
-      </c>
-      <c r="B428" t="s">
-        <v>679</v>
-      </c>
-      <c r="C428" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="429" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A429" t="s">
-        <v>247</v>
-      </c>
-      <c r="B429" t="s">
-        <v>679</v>
-      </c>
-      <c r="C429" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="430" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A430" t="s">
-        <v>247</v>
-      </c>
-      <c r="B430" t="s">
-        <v>679</v>
-      </c>
-      <c r="C430" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="431" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A431" t="s">
-        <v>247</v>
-      </c>
-      <c r="B431" t="s">
-        <v>679</v>
-      </c>
-      <c r="C431" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="432" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A432" t="s">
-        <v>247</v>
-      </c>
-      <c r="B432" t="s">
-        <v>679</v>
-      </c>
-      <c r="C432" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="433" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A433" t="s">
-        <v>247</v>
-      </c>
-      <c r="B433" t="s">
-        <v>679</v>
-      </c>
-      <c r="C433" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="434" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A434" t="s">
-        <v>247</v>
-      </c>
-      <c r="B434" t="s">
-        <v>679</v>
-      </c>
-      <c r="C434" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="435" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A435" t="s">
-        <v>247</v>
-      </c>
-      <c r="B435" t="s">
-        <v>679</v>
-      </c>
-      <c r="C435" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="436" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A436" t="s">
-        <v>247</v>
-      </c>
-      <c r="B436" t="s">
-        <v>679</v>
-      </c>
-      <c r="C436" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="437" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A437" t="s">
-        <v>247</v>
-      </c>
-      <c r="B437" t="s">
-        <v>679</v>
-      </c>
-      <c r="C437" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="438" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A438" t="s">
-        <v>247</v>
-      </c>
-      <c r="B438" t="s">
-        <v>679</v>
-      </c>
-      <c r="C438" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="439" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A439" t="s">
-        <v>247</v>
-      </c>
-      <c r="B439" t="s">
-        <v>679</v>
-      </c>
-      <c r="C439" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="440" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A440" t="s">
-        <v>247</v>
-      </c>
-      <c r="B440" t="s">
-        <v>679</v>
-      </c>
-      <c r="C440" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="441" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A441" t="s">
-        <v>247</v>
-      </c>
-      <c r="B441" t="s">
-        <v>679</v>
-      </c>
-      <c r="C441" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="442" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A442" t="s">
-        <v>247</v>
-      </c>
-      <c r="B442" t="s">
-        <v>679</v>
-      </c>
-      <c r="C442" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="443" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A443" t="s">
-        <v>247</v>
-      </c>
-      <c r="B443" t="s">
-        <v>679</v>
-      </c>
-      <c r="C443" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="444" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A444" t="s">
-        <v>247</v>
-      </c>
-      <c r="B444" t="s">
-        <v>679</v>
-      </c>
-      <c r="C444" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="445" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A445" t="s">
-        <v>247</v>
-      </c>
-      <c r="B445" t="s">
-        <v>679</v>
-      </c>
-      <c r="C445" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="446" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A446" t="s">
-        <v>247</v>
-      </c>
-      <c r="B446" t="s">
-        <v>679</v>
-      </c>
-      <c r="C446" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="447" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A447" t="s">
-        <v>247</v>
-      </c>
-      <c r="B447" t="s">
-        <v>679</v>
-      </c>
-      <c r="C447" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="448" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A448" t="s">
-        <v>247</v>
-      </c>
-      <c r="B448" t="s">
-        <v>679</v>
-      </c>
-      <c r="C448" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="449" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A449" t="s">
-        <v>247</v>
-      </c>
-      <c r="B449" t="s">
-        <v>679</v>
-      </c>
-      <c r="C449" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="450" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A450" t="s">
-        <v>247</v>
-      </c>
-      <c r="B450" t="s">
-        <v>679</v>
-      </c>
-      <c r="C450" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="451" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A451" t="s">
-        <v>247</v>
-      </c>
-      <c r="B451" t="s">
-        <v>679</v>
-      </c>
-      <c r="C451" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="452" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A452" t="s">
-        <v>247</v>
-      </c>
-      <c r="B452" t="s">
-        <v>679</v>
-      </c>
-      <c r="C452" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="453" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A453" t="s">
-        <v>247</v>
-      </c>
-      <c r="B453" t="s">
-        <v>679</v>
-      </c>
-      <c r="C453" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="454" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A454" t="s">
-        <v>247</v>
-      </c>
-      <c r="B454" t="s">
-        <v>679</v>
-      </c>
-      <c r="C454" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="455" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A455" t="s">
-        <v>247</v>
-      </c>
-      <c r="B455" t="s">
-        <v>679</v>
-      </c>
-      <c r="C455" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="456" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A456" t="s">
-        <v>247</v>
-      </c>
-      <c r="B456" t="s">
-        <v>679</v>
-      </c>
-      <c r="C456" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="457" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A457" t="s">
-        <v>247</v>
-      </c>
-      <c r="B457" t="s">
-        <v>679</v>
-      </c>
-      <c r="C457" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="458" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A458" t="s">
-        <v>247</v>
-      </c>
-      <c r="B458" t="s">
-        <v>679</v>
-      </c>
-      <c r="C458" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="459" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A459" t="s">
-        <v>247</v>
-      </c>
-      <c r="B459" t="s">
-        <v>679</v>
-      </c>
-      <c r="C459" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="460" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A460" t="s">
-        <v>247</v>
-      </c>
-      <c r="B460" t="s">
-        <v>679</v>
-      </c>
-      <c r="C460" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="461" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A461" t="s">
-        <v>247</v>
-      </c>
-      <c r="B461" t="s">
-        <v>679</v>
-      </c>
-      <c r="C461" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="462" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A462" t="s">
-        <v>247</v>
-      </c>
-      <c r="B462" t="s">
-        <v>679</v>
-      </c>
-      <c r="C462" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="463" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A463" t="s">
-        <v>247</v>
-      </c>
-      <c r="B463" t="s">
-        <v>679</v>
-      </c>
-      <c r="C463" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="464" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A464" t="s">
-        <v>247</v>
-      </c>
-      <c r="B464" t="s">
-        <v>679</v>
-      </c>
-      <c r="C464" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="465" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A465" t="s">
-        <v>247</v>
-      </c>
-      <c r="B465" t="s">
-        <v>679</v>
-      </c>
-      <c r="C465" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="466" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A466" t="s">
-        <v>247</v>
-      </c>
-      <c r="B466" t="s">
-        <v>679</v>
-      </c>
-      <c r="C466" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="467" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A467" t="s">
-        <v>247</v>
-      </c>
-      <c r="B467" t="s">
-        <v>679</v>
-      </c>
-      <c r="C467" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="468" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A468" t="s">
-        <v>247</v>
-      </c>
-      <c r="B468" t="s">
-        <v>679</v>
-      </c>
-      <c r="C468" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="469" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A469" t="s">
-        <v>247</v>
-      </c>
-      <c r="B469" t="s">
-        <v>679</v>
-      </c>
-      <c r="C469" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="470" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A470" t="s">
-        <v>247</v>
-      </c>
-      <c r="B470" t="s">
-        <v>679</v>
-      </c>
-      <c r="C470" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="471" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A471" t="s">
-        <v>247</v>
-      </c>
-      <c r="B471" t="s">
-        <v>679</v>
-      </c>
-      <c r="C471" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="472" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A472" t="s">
-        <v>247</v>
-      </c>
-      <c r="B472" t="s">
-        <v>679</v>
-      </c>
-      <c r="C472" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="473" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A473" t="s">
-        <v>247</v>
-      </c>
-      <c r="B473" t="s">
-        <v>679</v>
-      </c>
-      <c r="C473" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="474" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A474" t="s">
-        <v>247</v>
-      </c>
-      <c r="B474" t="s">
-        <v>679</v>
-      </c>
-      <c r="C474" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="475" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A475" t="s">
-        <v>247</v>
-      </c>
-      <c r="B475" t="s">
-        <v>679</v>
-      </c>
-      <c r="C475" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="476" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A476" t="s">
-        <v>247</v>
-      </c>
-      <c r="B476" t="s">
-        <v>679</v>
-      </c>
-      <c r="C476" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="477" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="D476" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
         <v>247</v>
       </c>
@@ -8182,10 +8414,13 @@
         <v>679</v>
       </c>
       <c r="C477" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="478" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>483</v>
+      </c>
+      <c r="D477" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="478" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
         <v>247</v>
       </c>
@@ -8193,10 +8428,13 @@
         <v>679</v>
       </c>
       <c r="C478" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="479" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>482</v>
+      </c>
+      <c r="D478" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
         <v>247</v>
       </c>
@@ -8204,10 +8442,13 @@
         <v>679</v>
       </c>
       <c r="C479" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="480" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>484</v>
+      </c>
+      <c r="D479" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
         <v>247</v>
       </c>
@@ -8215,10 +8456,13 @@
         <v>679</v>
       </c>
       <c r="C480" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="481" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>485</v>
+      </c>
+      <c r="D480" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
         <v>247</v>
       </c>
@@ -8226,10 +8470,13 @@
         <v>679</v>
       </c>
       <c r="C481" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="482" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>486</v>
+      </c>
+      <c r="D481" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="482" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
         <v>247</v>
       </c>
@@ -8237,10 +8484,13 @@
         <v>679</v>
       </c>
       <c r="C482" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="483" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>487</v>
+      </c>
+      <c r="D482" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="483" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
         <v>247</v>
       </c>
@@ -8248,10 +8498,13 @@
         <v>679</v>
       </c>
       <c r="C483" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="484" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>493</v>
+      </c>
+      <c r="D483" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="484" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
         <v>247</v>
       </c>
@@ -8259,10 +8512,13 @@
         <v>679</v>
       </c>
       <c r="C484" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="485" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>489</v>
+      </c>
+      <c r="D484" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="485" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
         <v>247</v>
       </c>
@@ -8272,8 +8528,11 @@
       <c r="C485" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="486" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="D485" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="486" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
         <v>247</v>
       </c>
@@ -8281,10 +8540,13 @@
         <v>679</v>
       </c>
       <c r="C486" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="487" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>492</v>
+      </c>
+      <c r="D486" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="487" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
         <v>247</v>
       </c>
@@ -8294,8 +8556,11 @@
       <c r="C487" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="488" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="D487" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="488" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
         <v>247</v>
       </c>
@@ -8305,8 +8570,11 @@
       <c r="C488" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="489" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="D488" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="489" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
         <v>247</v>
       </c>
@@ -8314,10 +8582,13 @@
         <v>679</v>
       </c>
       <c r="C489" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="490" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>494</v>
+      </c>
+      <c r="D489" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="490" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
         <v>247</v>
       </c>
@@ -8325,10 +8596,13 @@
         <v>679</v>
       </c>
       <c r="C490" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="491" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>495</v>
+      </c>
+      <c r="D490" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="491" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
         <v>247</v>
       </c>
@@ -8336,10 +8610,13 @@
         <v>679</v>
       </c>
       <c r="C491" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="492" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>496</v>
+      </c>
+      <c r="D491" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="492" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
         <v>247</v>
       </c>
@@ -8347,10 +8624,13 @@
         <v>679</v>
       </c>
       <c r="C492" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="493" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>497</v>
+      </c>
+      <c r="D492" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="493" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
         <v>247</v>
       </c>
@@ -8358,10 +8638,13 @@
         <v>679</v>
       </c>
       <c r="C493" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="494" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>498</v>
+      </c>
+      <c r="D493" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="494" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
         <v>247</v>
       </c>
@@ -8369,10 +8652,13 @@
         <v>679</v>
       </c>
       <c r="C494" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="495" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>499</v>
+      </c>
+      <c r="D494" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="495" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
         <v>247</v>
       </c>
@@ -8380,10 +8666,13 @@
         <v>679</v>
       </c>
       <c r="C495" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="496" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>500</v>
+      </c>
+      <c r="D495" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="496" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
         <v>247</v>
       </c>
@@ -8391,10 +8680,13 @@
         <v>679</v>
       </c>
       <c r="C496" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="497" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>501</v>
+      </c>
+      <c r="D496" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="497" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
         <v>247</v>
       </c>
@@ -8402,10 +8694,13 @@
         <v>679</v>
       </c>
       <c r="C497" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="498" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>502</v>
+      </c>
+      <c r="D497" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="498" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
         <v>247</v>
       </c>
@@ -8413,10 +8708,13 @@
         <v>679</v>
       </c>
       <c r="C498" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="499" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>503</v>
+      </c>
+      <c r="D498" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="499" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
         <v>247</v>
       </c>
@@ -8424,10 +8722,13 @@
         <v>679</v>
       </c>
       <c r="C499" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="500" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>504</v>
+      </c>
+      <c r="D499" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="500" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
         <v>247</v>
       </c>
@@ -8435,10 +8736,13 @@
         <v>679</v>
       </c>
       <c r="C500" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="501" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>505</v>
+      </c>
+      <c r="D500" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="501" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
         <v>247</v>
       </c>
@@ -8446,10 +8750,13 @@
         <v>679</v>
       </c>
       <c r="C501" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="502" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>506</v>
+      </c>
+      <c r="D501" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="502" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
         <v>247</v>
       </c>
@@ -8457,10 +8764,13 @@
         <v>679</v>
       </c>
       <c r="C502" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="503" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>507</v>
+      </c>
+      <c r="D502" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="503" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
         <v>247</v>
       </c>
@@ -8468,10 +8778,13 @@
         <v>679</v>
       </c>
       <c r="C503" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="504" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>574</v>
+      </c>
+      <c r="D503" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="504" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
         <v>247</v>
       </c>
@@ -8479,10 +8792,13 @@
         <v>679</v>
       </c>
       <c r="C504" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="505" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>576</v>
+      </c>
+      <c r="D504" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="505" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
         <v>247</v>
       </c>
@@ -8493,7 +8809,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="506" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
         <v>247</v>
       </c>
@@ -8504,7 +8820,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="507" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
         <v>247</v>
       </c>
@@ -8515,7 +8831,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="508" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
         <v>247</v>
       </c>
@@ -8526,7 +8842,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="509" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
         <v>247</v>
       </c>
@@ -8537,7 +8853,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="510" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
         <v>247</v>
       </c>
@@ -8548,7 +8864,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="511" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
         <v>247</v>
       </c>
@@ -8559,7 +8875,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="512" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
         <v>247</v>
       </c>
@@ -9098,7 +9414,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="561" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
         <v>247</v>
       </c>
@@ -9109,7 +9425,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="562" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
         <v>247</v>
       </c>
@@ -9120,7 +9436,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="563" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
         <v>247</v>
       </c>
@@ -9131,7 +9447,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="564" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
         <v>247</v>
       </c>
@@ -9142,7 +9458,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="565" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
         <v>247</v>
       </c>
@@ -9153,7 +9469,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="566" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
         <v>247</v>
       </c>
@@ -9164,7 +9480,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="567" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
         <v>247</v>
       </c>
@@ -9175,7 +9491,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="568" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
         <v>247</v>
       </c>
@@ -9186,7 +9502,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="569" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
         <v>247</v>
       </c>
@@ -9197,7 +9513,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="570" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
         <v>247</v>
       </c>
@@ -9208,7 +9524,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="571" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
         <v>247</v>
       </c>
@@ -9216,10 +9532,13 @@
         <v>679</v>
       </c>
       <c r="C571" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="572" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>577</v>
+      </c>
+      <c r="D571" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="572" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
         <v>247</v>
       </c>
@@ -9229,8 +9548,11 @@
       <c r="C572" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="573" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="D572" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="573" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A573" t="s">
         <v>247</v>
       </c>
@@ -9238,10 +9560,13 @@
         <v>679</v>
       </c>
       <c r="C573" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="574" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>578</v>
+      </c>
+      <c r="D573" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="574" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A574" t="s">
         <v>247</v>
       </c>
@@ -9249,10 +9574,13 @@
         <v>679</v>
       </c>
       <c r="C574" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="575" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>579</v>
+      </c>
+      <c r="D574" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="575" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A575" t="s">
         <v>247</v>
       </c>
@@ -9260,10 +9588,13 @@
         <v>679</v>
       </c>
       <c r="C575" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="576" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>580</v>
+      </c>
+      <c r="D575" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="576" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
         <v>247</v>
       </c>
@@ -9271,10 +9602,13 @@
         <v>679</v>
       </c>
       <c r="C576" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="577" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>581</v>
+      </c>
+      <c r="D576" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="577" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
         <v>247</v>
       </c>
@@ -9282,10 +9616,13 @@
         <v>679</v>
       </c>
       <c r="C577" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="578" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>582</v>
+      </c>
+      <c r="D577" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="578" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
         <v>247</v>
       </c>
@@ -9293,10 +9630,13 @@
         <v>679</v>
       </c>
       <c r="C578" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="579" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>583</v>
+      </c>
+      <c r="D578" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="579" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A579" t="s">
         <v>247</v>
       </c>
@@ -9304,32 +9644,41 @@
         <v>679</v>
       </c>
       <c r="C579" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="580" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>584</v>
+      </c>
+      <c r="D579" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="580" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A580" t="s">
-        <v>247</v>
+        <v>220</v>
       </c>
       <c r="B580" t="s">
         <v>679</v>
       </c>
       <c r="C580" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="581" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+      <c r="D580" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="581" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A581" t="s">
-        <v>247</v>
+        <v>220</v>
       </c>
       <c r="B581" t="s">
         <v>679</v>
       </c>
       <c r="C581" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="582" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+        <v>229</v>
+      </c>
+      <c r="D581" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="582" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A582" t="s">
         <v>247</v>
       </c>
@@ -9340,7 +9689,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="583" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
         <v>247</v>
       </c>
@@ -9351,7 +9700,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="584" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
         <v>247</v>
       </c>
@@ -9362,7 +9711,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="585" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A585" t="s">
         <v>247</v>
       </c>
@@ -9373,7 +9722,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="586" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
         <v>247</v>
       </c>
@@ -9384,7 +9733,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="587" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A587" t="s">
         <v>247</v>
       </c>
@@ -9392,340 +9741,382 @@
         <v>679</v>
       </c>
       <c r="C587" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="588" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A588" t="s">
+        <v>247</v>
+      </c>
+      <c r="B588" t="s">
+        <v>679</v>
+      </c>
+      <c r="C588" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="589" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A589" t="s">
+        <v>247</v>
+      </c>
+      <c r="B589" t="s">
+        <v>679</v>
+      </c>
+      <c r="C589" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="588" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A588" t="s">
-        <v>247</v>
-      </c>
-      <c r="B588" t="s">
-        <v>679</v>
-      </c>
-      <c r="C588" t="s">
+    <row r="590" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A590" t="s">
+        <v>247</v>
+      </c>
+      <c r="B590" t="s">
+        <v>679</v>
+      </c>
+      <c r="C590" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="589" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A589" t="s">
-        <v>247</v>
-      </c>
-      <c r="B589" t="s">
-        <v>679</v>
-      </c>
-      <c r="C589" t="s">
+    <row r="591" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A591" t="s">
+        <v>247</v>
+      </c>
+      <c r="B591" t="s">
+        <v>679</v>
+      </c>
+      <c r="C591" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="590" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A590" t="s">
-        <v>247</v>
-      </c>
-      <c r="B590" t="s">
-        <v>679</v>
-      </c>
-      <c r="C590" t="s">
+    <row r="592" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A592" t="s">
+        <v>247</v>
+      </c>
+      <c r="B592" t="s">
+        <v>679</v>
+      </c>
+      <c r="C592" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="593" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A593" t="s">
+        <v>247</v>
+      </c>
+      <c r="B593" t="s">
+        <v>679</v>
+      </c>
+      <c r="C593" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="594" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A594" t="s">
+        <v>247</v>
+      </c>
+      <c r="B594" t="s">
+        <v>679</v>
+      </c>
+      <c r="C594" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="595" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A595" t="s">
+        <v>247</v>
+      </c>
+      <c r="B595" t="s">
+        <v>679</v>
+      </c>
+      <c r="C595" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="596" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A596" t="s">
+        <v>247</v>
+      </c>
+      <c r="B596" t="s">
+        <v>679</v>
+      </c>
+      <c r="C596" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="591" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A591" t="s">
-        <v>247</v>
-      </c>
-      <c r="B591" t="s">
-        <v>679</v>
-      </c>
-      <c r="C591" t="s">
+    <row r="597" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A597" t="s">
+        <v>247</v>
+      </c>
+      <c r="B597" t="s">
+        <v>679</v>
+      </c>
+      <c r="D597" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="592" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A592" t="s">
-        <v>247</v>
-      </c>
-      <c r="B592" t="s">
-        <v>679</v>
-      </c>
-      <c r="C592" t="s">
+    <row r="598" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A598" t="s">
+        <v>247</v>
+      </c>
+      <c r="B598" t="s">
+        <v>679</v>
+      </c>
+      <c r="C598" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="593" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A593" t="s">
-        <v>247</v>
-      </c>
-      <c r="B593" t="s">
-        <v>679</v>
-      </c>
-      <c r="C593" t="s">
+      <c r="D598" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="599" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A599" t="s">
+        <v>247</v>
+      </c>
+      <c r="B599" t="s">
+        <v>679</v>
+      </c>
+      <c r="C599" t="s">
         <v>596</v>
       </c>
-    </row>
-    <row r="594" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A594" t="s">
-        <v>247</v>
-      </c>
-      <c r="B594" t="s">
-        <v>679</v>
-      </c>
-      <c r="C594" t="s">
+      <c r="D599" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="600" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A600" t="s">
+        <v>247</v>
+      </c>
+      <c r="B600" t="s">
+        <v>679</v>
+      </c>
+      <c r="C600" t="s">
         <v>597</v>
       </c>
-    </row>
-    <row r="595" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A595" t="s">
-        <v>247</v>
-      </c>
-      <c r="B595" t="s">
-        <v>679</v>
-      </c>
-      <c r="C595" t="s">
+      <c r="D600" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="601" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A601" t="s">
+        <v>247</v>
+      </c>
+      <c r="B601" t="s">
+        <v>679</v>
+      </c>
+      <c r="C601" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="596" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A596" t="s">
-        <v>247</v>
-      </c>
-      <c r="B596" t="s">
-        <v>679</v>
-      </c>
-      <c r="C596" t="s">
+      <c r="D601" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="602" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A602" t="s">
+        <v>247</v>
+      </c>
+      <c r="B602" t="s">
+        <v>679</v>
+      </c>
+      <c r="C602" t="s">
         <v>599</v>
       </c>
-    </row>
-    <row r="597" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A597" t="s">
-        <v>247</v>
-      </c>
-      <c r="B597" t="s">
-        <v>679</v>
-      </c>
-      <c r="C597" t="s">
+      <c r="D602" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="603" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A603" t="s">
+        <v>247</v>
+      </c>
+      <c r="B603" t="s">
+        <v>679</v>
+      </c>
+      <c r="C603" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="598" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A598" t="s">
-        <v>247</v>
-      </c>
-      <c r="B598" t="s">
-        <v>679</v>
-      </c>
-      <c r="C598" t="s">
+      <c r="D603" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="604" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A604" t="s">
+        <v>247</v>
+      </c>
+      <c r="B604" t="s">
+        <v>679</v>
+      </c>
+      <c r="C604" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="599" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A599" t="s">
-        <v>247</v>
-      </c>
-      <c r="B599" t="s">
-        <v>679</v>
-      </c>
-      <c r="C599" t="s">
+      <c r="D604" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="605" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A605" t="s">
+        <v>247</v>
+      </c>
+      <c r="B605" t="s">
+        <v>679</v>
+      </c>
+      <c r="C605" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="600" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A600" t="s">
-        <v>247</v>
-      </c>
-      <c r="B600" t="s">
-        <v>679</v>
-      </c>
-      <c r="C600" t="s">
+      <c r="D605" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="606" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A606" t="s">
+        <v>247</v>
+      </c>
+      <c r="B606" t="s">
+        <v>679</v>
+      </c>
+      <c r="C606" t="s">
         <v>603</v>
       </c>
-    </row>
-    <row r="601" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A601" t="s">
-        <v>247</v>
-      </c>
-      <c r="B601" t="s">
-        <v>679</v>
-      </c>
-      <c r="C601" t="s">
+      <c r="D606" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="607" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A607" t="s">
+        <v>247</v>
+      </c>
+      <c r="B607" t="s">
+        <v>679</v>
+      </c>
+      <c r="C607" t="s">
         <v>604</v>
       </c>
-    </row>
-    <row r="602" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A602" t="s">
-        <v>247</v>
-      </c>
-      <c r="B602" t="s">
-        <v>679</v>
-      </c>
-      <c r="C602" t="s">
+      <c r="D607" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="608" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A608" t="s">
+        <v>247</v>
+      </c>
+      <c r="B608" t="s">
+        <v>679</v>
+      </c>
+      <c r="C608" t="s">
         <v>605</v>
       </c>
-    </row>
-    <row r="603" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A603" t="s">
-        <v>247</v>
-      </c>
-      <c r="B603" t="s">
-        <v>679</v>
-      </c>
-      <c r="C603" t="s">
+      <c r="D608" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="609" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A609" t="s">
+        <v>247</v>
+      </c>
+      <c r="B609" t="s">
+        <v>679</v>
+      </c>
+      <c r="C609" t="s">
         <v>606</v>
       </c>
-    </row>
-    <row r="604" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A604" t="s">
-        <v>247</v>
-      </c>
-      <c r="B604" t="s">
-        <v>679</v>
-      </c>
-      <c r="C604" t="s">
+      <c r="D609" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="610" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A610" t="s">
+        <v>247</v>
+      </c>
+      <c r="B610" t="s">
+        <v>679</v>
+      </c>
+      <c r="C610" t="s">
+        <v>615</v>
+      </c>
+      <c r="D610" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="611" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A611" t="s">
+        <v>247</v>
+      </c>
+      <c r="B611" t="s">
+        <v>679</v>
+      </c>
+      <c r="C611" t="s">
+        <v>616</v>
+      </c>
+      <c r="D611" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="612" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A612" t="s">
+        <v>247</v>
+      </c>
+      <c r="B612" t="s">
+        <v>679</v>
+      </c>
+      <c r="C612" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="613" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A613" t="s">
+        <v>247</v>
+      </c>
+      <c r="B613" t="s">
+        <v>679</v>
+      </c>
+      <c r="C613" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="614" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A614" t="s">
+        <v>247</v>
+      </c>
+      <c r="B614" t="s">
+        <v>679</v>
+      </c>
+      <c r="C614" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="615" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A615" t="s">
+        <v>247</v>
+      </c>
+      <c r="B615" t="s">
+        <v>679</v>
+      </c>
+      <c r="C615" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="616" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A616" t="s">
+        <v>247</v>
+      </c>
+      <c r="B616" t="s">
+        <v>679</v>
+      </c>
+      <c r="C616" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="605" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A605" t="s">
-        <v>247</v>
-      </c>
-      <c r="B605" t="s">
-        <v>679</v>
-      </c>
-      <c r="C605" t="s">
+    <row r="617" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A617" t="s">
+        <v>247</v>
+      </c>
+      <c r="B617" t="s">
+        <v>679</v>
+      </c>
+      <c r="C617" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="606" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A606" t="s">
-        <v>247</v>
-      </c>
-      <c r="B606" t="s">
-        <v>679</v>
-      </c>
-      <c r="C606" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="607" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A607" t="s">
-        <v>247</v>
-      </c>
-      <c r="B607" t="s">
-        <v>679</v>
-      </c>
-      <c r="C607" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="608" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A608" t="s">
-        <v>247</v>
-      </c>
-      <c r="B608" t="s">
-        <v>679</v>
-      </c>
-      <c r="C608" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="609" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A609" t="s">
-        <v>247</v>
-      </c>
-      <c r="B609" t="s">
-        <v>679</v>
-      </c>
-      <c r="C609" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="610" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A610" t="s">
-        <v>247</v>
-      </c>
-      <c r="B610" t="s">
-        <v>679</v>
-      </c>
-      <c r="C610" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="611" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A611" t="s">
-        <v>247</v>
-      </c>
-      <c r="B611" t="s">
-        <v>679</v>
-      </c>
-      <c r="C611" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="612" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A612" t="s">
-        <v>247</v>
-      </c>
-      <c r="B612" t="s">
-        <v>679</v>
-      </c>
-      <c r="C612" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="613" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A613" t="s">
-        <v>247</v>
-      </c>
-      <c r="B613" t="s">
-        <v>679</v>
-      </c>
-      <c r="C613" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="614" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A614" t="s">
-        <v>247</v>
-      </c>
-      <c r="B614" t="s">
-        <v>679</v>
-      </c>
-      <c r="C614" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="615" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A615" t="s">
-        <v>247</v>
-      </c>
-      <c r="B615" t="s">
-        <v>679</v>
-      </c>
-      <c r="C615" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="616" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A616" t="s">
-        <v>247</v>
-      </c>
-      <c r="B616" t="s">
-        <v>679</v>
-      </c>
-      <c r="C616" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="617" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A617" t="s">
-        <v>247</v>
-      </c>
-      <c r="B617" t="s">
-        <v>679</v>
-      </c>
-      <c r="C617" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="618" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A618" t="s">
         <v>247</v>
       </c>
@@ -9736,7 +10127,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="619" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A619" t="s">
         <v>247</v>
       </c>
@@ -9744,65 +10135,65 @@
         <v>679</v>
       </c>
       <c r="C619" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="620" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A620" t="s">
+        <v>247</v>
+      </c>
+      <c r="B620" t="s">
+        <v>679</v>
+      </c>
+      <c r="C620" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="621" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A621" t="s">
+        <v>247</v>
+      </c>
+      <c r="B621" t="s">
+        <v>679</v>
+      </c>
+      <c r="C621" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="622" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A622" t="s">
+        <v>247</v>
+      </c>
+      <c r="B622" t="s">
+        <v>679</v>
+      </c>
+      <c r="C622" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="623" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A623" t="s">
+        <v>247</v>
+      </c>
+      <c r="B623" t="s">
+        <v>679</v>
+      </c>
+      <c r="C623" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="624" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A624" t="s">
+        <v>247</v>
+      </c>
+      <c r="B624" t="s">
+        <v>679</v>
+      </c>
+      <c r="C624" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="620" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A620" t="s">
-        <v>247</v>
-      </c>
-      <c r="B620" t="s">
-        <v>679</v>
-      </c>
-      <c r="C620" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="621" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A621" t="s">
-        <v>247</v>
-      </c>
-      <c r="B621" t="s">
-        <v>679</v>
-      </c>
-      <c r="C621" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="622" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A622" t="s">
-        <v>247</v>
-      </c>
-      <c r="B622" t="s">
-        <v>679</v>
-      </c>
-      <c r="C622" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="623" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A623" t="s">
-        <v>247</v>
-      </c>
-      <c r="B623" t="s">
-        <v>679</v>
-      </c>
-      <c r="C623" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="624" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A624" t="s">
-        <v>247</v>
-      </c>
-      <c r="B624" t="s">
-        <v>679</v>
-      </c>
-      <c r="C624" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="625" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A625" t="s">
         <v>247</v>
       </c>
@@ -9813,7 +10204,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="626" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A626" t="s">
         <v>247</v>
       </c>
@@ -9824,7 +10215,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="627" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A627" t="s">
         <v>247</v>
       </c>
@@ -9835,7 +10226,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="628" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A628" t="s">
         <v>247</v>
       </c>
@@ -9846,7 +10237,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="629" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" t="s">
         <v>247</v>
       </c>
@@ -9857,7 +10248,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="630" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A630" t="s">
         <v>247</v>
       </c>
@@ -9868,7 +10259,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="631" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A631" t="s">
         <v>247</v>
       </c>
@@ -9879,7 +10270,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="632" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A632" t="s">
         <v>247</v>
       </c>
@@ -9890,7 +10281,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="633" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A633" t="s">
         <v>247</v>
       </c>
@@ -9901,7 +10292,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="634" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A634" t="s">
         <v>247</v>
       </c>
@@ -9912,7 +10303,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="635" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A635" t="s">
         <v>247</v>
       </c>
@@ -9923,7 +10314,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="636" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A636" t="s">
         <v>247</v>
       </c>
@@ -9934,7 +10325,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="637" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A637" t="s">
         <v>247</v>
       </c>
@@ -9945,7 +10336,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="638" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A638" t="s">
         <v>247</v>
       </c>
@@ -9956,7 +10347,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="639" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A639" t="s">
         <v>247</v>
       </c>
@@ -9964,131 +10355,131 @@
         <v>679</v>
       </c>
       <c r="C639" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="640" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A640" t="s">
+        <v>247</v>
+      </c>
+      <c r="B640" t="s">
+        <v>679</v>
+      </c>
+      <c r="C640" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="641" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A641" t="s">
+        <v>247</v>
+      </c>
+      <c r="B641" t="s">
+        <v>679</v>
+      </c>
+      <c r="C641" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="642" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A642" t="s">
+        <v>247</v>
+      </c>
+      <c r="B642" t="s">
+        <v>679</v>
+      </c>
+      <c r="C642" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="643" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A643" t="s">
+        <v>247</v>
+      </c>
+      <c r="B643" t="s">
+        <v>679</v>
+      </c>
+      <c r="C643" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="644" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A644" t="s">
+        <v>247</v>
+      </c>
+      <c r="B644" t="s">
+        <v>679</v>
+      </c>
+      <c r="C644" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="645" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A645" t="s">
+        <v>247</v>
+      </c>
+      <c r="B645" t="s">
+        <v>679</v>
+      </c>
+      <c r="C645" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="640" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A640" t="s">
-        <v>247</v>
-      </c>
-      <c r="B640" t="s">
-        <v>679</v>
-      </c>
-      <c r="C640" t="s">
+    <row r="646" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A646" t="s">
+        <v>247</v>
+      </c>
+      <c r="B646" t="s">
+        <v>679</v>
+      </c>
+      <c r="C646" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="641" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A641" t="s">
-        <v>247</v>
-      </c>
-      <c r="B641" t="s">
-        <v>679</v>
-      </c>
-      <c r="C641" t="s">
+    <row r="647" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A647" t="s">
+        <v>247</v>
+      </c>
+      <c r="B647" t="s">
+        <v>679</v>
+      </c>
+      <c r="C647" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="642" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A642" t="s">
-        <v>247</v>
-      </c>
-      <c r="B642" t="s">
-        <v>679</v>
-      </c>
-      <c r="C642" t="s">
+    <row r="648" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A648" t="s">
+        <v>247</v>
+      </c>
+      <c r="B648" t="s">
+        <v>679</v>
+      </c>
+      <c r="C648" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="643" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A643" t="s">
-        <v>247</v>
-      </c>
-      <c r="B643" t="s">
-        <v>679</v>
-      </c>
-      <c r="C643" t="s">
+    <row r="649" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A649" t="s">
+        <v>247</v>
+      </c>
+      <c r="B649" t="s">
+        <v>679</v>
+      </c>
+      <c r="C649" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="644" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A644" t="s">
-        <v>247</v>
-      </c>
-      <c r="B644" t="s">
-        <v>679</v>
-      </c>
-      <c r="C644" t="s">
+    <row r="650" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A650" t="s">
+        <v>247</v>
+      </c>
+      <c r="B650" t="s">
+        <v>679</v>
+      </c>
+      <c r="C650" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="645" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A645" t="s">
-        <v>247</v>
-      </c>
-      <c r="B645" t="s">
-        <v>679</v>
-      </c>
-      <c r="C645" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="646" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A646" t="s">
-        <v>247</v>
-      </c>
-      <c r="B646" t="s">
-        <v>679</v>
-      </c>
-      <c r="C646" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="647" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A647" t="s">
-        <v>247</v>
-      </c>
-      <c r="B647" t="s">
-        <v>679</v>
-      </c>
-      <c r="C647" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="648" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A648" t="s">
-        <v>247</v>
-      </c>
-      <c r="B648" t="s">
-        <v>679</v>
-      </c>
-      <c r="C648" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="649" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A649" t="s">
-        <v>247</v>
-      </c>
-      <c r="B649" t="s">
-        <v>679</v>
-      </c>
-      <c r="C649" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="650" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A650" t="s">
-        <v>247</v>
-      </c>
-      <c r="B650" t="s">
-        <v>679</v>
-      </c>
-      <c r="C650" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="651" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" t="s">
         <v>247</v>
       </c>
@@ -10099,7 +10490,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="652" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A652" t="s">
         <v>247</v>
       </c>
@@ -10110,7 +10501,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="653" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A653" t="s">
         <v>247</v>
       </c>
@@ -10121,7 +10512,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="654" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A654" t="s">
         <v>247</v>
       </c>
@@ -10132,7 +10523,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="655" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A655" t="s">
         <v>247</v>
       </c>
@@ -10143,7 +10534,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="656" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A656" t="s">
         <v>247</v>
       </c>
@@ -10154,7 +10545,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="657" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A657" t="s">
         <v>247</v>
       </c>
@@ -10165,7 +10556,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="658" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A658" t="s">
         <v>247</v>
       </c>
@@ -10173,98 +10564,98 @@
         <v>679</v>
       </c>
       <c r="C658" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="659" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A659" t="s">
+        <v>247</v>
+      </c>
+      <c r="B659" t="s">
+        <v>679</v>
+      </c>
+      <c r="C659" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="660" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A660" t="s">
+        <v>247</v>
+      </c>
+      <c r="B660" t="s">
+        <v>679</v>
+      </c>
+      <c r="C660" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="661" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A661" t="s">
+        <v>247</v>
+      </c>
+      <c r="B661" t="s">
+        <v>679</v>
+      </c>
+      <c r="C661" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="662" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A662" t="s">
+        <v>247</v>
+      </c>
+      <c r="B662" t="s">
+        <v>679</v>
+      </c>
+      <c r="C662" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="663" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A663" t="s">
+        <v>247</v>
+      </c>
+      <c r="B663" t="s">
+        <v>679</v>
+      </c>
+      <c r="C663" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="664" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A664" t="s">
+        <v>247</v>
+      </c>
+      <c r="B664" t="s">
+        <v>679</v>
+      </c>
+      <c r="C664" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="665" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A665" t="s">
+        <v>247</v>
+      </c>
+      <c r="B665" t="s">
+        <v>679</v>
+      </c>
+      <c r="C665" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="666" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A666" t="s">
+        <v>247</v>
+      </c>
+      <c r="B666" t="s">
+        <v>679</v>
+      </c>
+      <c r="C666" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="659" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A659" t="s">
-        <v>247</v>
-      </c>
-      <c r="B659" t="s">
-        <v>679</v>
-      </c>
-      <c r="C659" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="660" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A660" t="s">
-        <v>247</v>
-      </c>
-      <c r="B660" t="s">
-        <v>679</v>
-      </c>
-      <c r="C660" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="661" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A661" t="s">
-        <v>247</v>
-      </c>
-      <c r="B661" t="s">
-        <v>679</v>
-      </c>
-      <c r="C661" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="662" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A662" t="s">
-        <v>247</v>
-      </c>
-      <c r="B662" t="s">
-        <v>679</v>
-      </c>
-      <c r="C662" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="663" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A663" t="s">
-        <v>247</v>
-      </c>
-      <c r="B663" t="s">
-        <v>679</v>
-      </c>
-      <c r="C663" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="664" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A664" t="s">
-        <v>247</v>
-      </c>
-      <c r="B664" t="s">
-        <v>679</v>
-      </c>
-      <c r="C664" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="665" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A665" t="s">
-        <v>247</v>
-      </c>
-      <c r="B665" t="s">
-        <v>679</v>
-      </c>
-      <c r="C665" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="666" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A666" t="s">
-        <v>247</v>
-      </c>
-      <c r="B666" t="s">
-        <v>679</v>
-      </c>
-      <c r="C666" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="667" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A667" t="s">
         <v>247</v>
       </c>
@@ -10275,7 +10666,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="668" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A668" t="s">
         <v>247</v>
       </c>
@@ -10286,7 +10677,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="669" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A669" t="s">
         <v>247</v>
       </c>
@@ -10297,7 +10688,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="670" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A670" t="s">
         <v>247</v>
       </c>
@@ -10308,7 +10699,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="671" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A671" t="s">
         <v>247</v>
       </c>
@@ -10318,8 +10709,11 @@
       <c r="C671" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="672" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+      <c r="D671" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="672" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A672" t="s">
         <v>247</v>
       </c>
@@ -10329,14 +10723,20 @@
       <c r="C672" t="s">
         <v>675</v>
       </c>
+      <c r="D672" t="s">
+        <v>674</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C672" xr:uid="{176C812C-05FE-6A4B-9762-43F5FB22FFF3}">
-    <filterColumn colId="0">
+  <autoFilter ref="A1:D672" xr:uid="{176C812C-05FE-6A4B-9762-43F5FB22FFF3}">
+    <filterColumn colId="1">
       <filters>
-        <filter val="High seas"/>
+        <filter val="West Coast"/>
       </filters>
     </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A226:D672">
+      <sortCondition ref="C1:C672"/>
+    </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
